--- a/cleaning_pipeline_R/dictionaries/dictionary_mwi_combined_maternity_outcomes.xlsx
+++ b/cleaning_pipeline_R/dictionaries/dictionary_mwi_combined_maternity_outcomes.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3668,6 +3668,177 @@
       <c r="R51" t="inlineStr">
         <is>
           <t>Derived canonical birth weight (grams). Cleaning pipeline Module 15 computes coalesce(birthweight, bwt, bwtdis) -- three names for the same concept across Neotree form/script versions (bwtdis is birth weight despite its name; sources are identical where they overlap). Emitted in every dataset (NA where no source column is present). Originals retained. Use this column for low-birth-weight analysis. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MWI_combined_maternity_outcomes</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Maternal age (years) -- canonical (derived)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>mat_age_years_combined</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>9</v>
+      </c>
+      <c r="Q52">
+        <v>60</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Derived canonical maternal age in years. Cleaning pipeline Module 15 computes coalesce(matageyrs, mat_age_date_years): the manually entered whole-year field wins, falling back to the value derived from matagedate (auto-calculated from DOB, stored in HOURS, converted to years and range-filtered in Module 11). Both inputs are already range-clean (9-60), so this is a lossless coalesce plus a provenance label. Emitted only where at least one source column is present. Rows where both sources are present and disagree by more than 1 year are counted and logged, never overwritten -- see the per-run report 15b_maternal_age_summary.txt. Provenance is in mat_age_source. Originals retained. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MWI_combined_maternity_outcomes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. One of: 'matageyrs' (manually entered whole years, the priority source), 'matagedate_derived' (converted from the auto-calculated DOB field in Module 11), or 'none' (neither source populated on that row). Use it to restrict an analysis to manually entered ages, or to quantify reliance on the derived fallback. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MWI_combined_maternity_outcomes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>mat_age_date_years</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Maternal age (years) from auto-calculated DOB field (derived)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>mat_age_date_years</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>9</v>
+      </c>
+      <c r="Q54">
+        <v>60</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Produced by **Module 11** (not Module 15) as round(matagedate / 8766), where 8766 = 365.25 x 24: matagedate is auto-calculated from the mother's date of birth and stored in HOURS, not years. The same 9-60 plausibility filter applied to matageyrs is applied here, with out-of-range values set to NA and counted in the Module 11 report; raw matagedate is left untouched. MWI maternity forms only -- ZIM does not capture matagedate. This is an intermediate: prefer mat_age_years_combined for analysis, and use this column only to inspect the auto-calculated source directly. Not a raw field; no .value column.</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11705,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11858,6 +12029,64 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MWI_combined_maternity_outcomes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Maternal age -- source of the derived value (provenance)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Derived (computed by cleaning pipeline Module 15)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mat_age_source</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Provenance label for mat_age_years_combined, emitted alongside it by Module 15. One of: 'matageyrs' (manually entered whole years, the priority source), 'matagedate_derived' (converted from the auto-calculated DOB field in Module 11), or 'none' (neither source populated on that row). Use it to restrict an analysis to manually entered ages, or to quantify reliance on the derived fallback. Not a raw field; no .value column.</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Categorical with no value map entries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
